--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0001T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0001T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>100.287255867391</v>
+        <v>16.29667907845103</v>
       </c>
       <c r="D2" t="n">
-        <v>77.31263980901211</v>
+        <v>12.56330396896447</v>
       </c>
       <c r="E2" t="n">
-        <v>31.00892472889919</v>
+        <v>5.038950268446119</v>
       </c>
       <c r="F2" t="n">
-        <v>28.41809486091338</v>
+        <v>4.617940414898424</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>66.61285336890933</v>
+        <v>10.82458867244777</v>
       </c>
       <c r="D3" t="n">
-        <v>15.09381172501525</v>
+        <v>2.452744405314978</v>
       </c>
       <c r="E3" t="n">
-        <v>31.00892472889919</v>
+        <v>5.038950268446119</v>
       </c>
       <c r="F3" t="n">
-        <v>28.41809486091338</v>
+        <v>4.617940414898424</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>86.4137118063002</v>
+        <v>14.04222816852378</v>
       </c>
       <c r="D4" t="n">
-        <v>60.47965942865669</v>
+        <v>9.827944657156712</v>
       </c>
       <c r="E4" t="n">
-        <v>31.00892472889919</v>
+        <v>5.038950268446119</v>
       </c>
       <c r="F4" t="n">
-        <v>28.41809486091338</v>
+        <v>4.617940414898424</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.02745122592587</v>
+        <v>4.879460824212954</v>
       </c>
       <c r="D5" t="n">
-        <v>10.22183273450085</v>
+        <v>1.661047819356388</v>
       </c>
       <c r="E5" t="n">
-        <v>31.00892472889919</v>
+        <v>5.038950268446119</v>
       </c>
       <c r="F5" t="n">
-        <v>28.41809486091338</v>
+        <v>4.617940414898424</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>20.65373693081656</v>
+        <v>3.356232251257691</v>
       </c>
       <c r="D6" t="n">
-        <v>10.74266376169158</v>
+        <v>1.745682861274881</v>
       </c>
       <c r="E6" t="n">
-        <v>31.00892472889919</v>
+        <v>5.038950268446119</v>
       </c>
       <c r="F6" t="n">
-        <v>28.41809486091338</v>
+        <v>4.617940414898424</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
